--- a/tools/_out/groupD_20261021/regen/stage/DesignTable_6701_SW2.xlsx
+++ b/tools/_out/groupD_20261021/regen/stage/DesignTable_6701_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV3"/>
+  <dimension ref="A1:BV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1038,32 +1038,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6701-12-12</t>
+          <t>6701-04-04</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.139997</v>
+        <v>0.747018</v>
       </c>
       <c r="C3" t="n">
-        <v>0.649519</v>
+        <v>0.288675</v>
       </c>
       <c r="D3" t="n">
-        <v>0.53125</v>
+        <v>0.21875</v>
       </c>
       <c r="E3" t="n">
-        <v>0.125</v>
+        <v>0.075</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3895</v>
+        <v>0.2608</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4715</v>
+        <v>0.182</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1299</v>
+        <v>0.0795</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1851</v>
+        <v>0.1135</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
@@ -1072,218 +1072,974 @@
         <v>37</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0625</v>
+        <v>0.4375</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08333</v>
+        <v>0.05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7045</v>
+        <v>0.4538</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04511</v>
+        <v>0.02706</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02083</v>
+        <v>0.0125</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.08333</v>
+        <v>0.05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.125</v>
+        <v>0.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0.863997</v>
+        <v>0.550018</v>
       </c>
       <c r="T3" t="n">
-        <v>0.276</v>
+        <v>0.197</v>
       </c>
       <c r="U3" t="n">
-        <v>0.863997</v>
+        <v>0.550018</v>
       </c>
       <c r="V3" t="n">
-        <v>1.319</v>
+        <v>0.896</v>
       </c>
       <c r="W3" t="n">
-        <v>1.181</v>
+        <v>0.354</v>
       </c>
       <c r="X3" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.909</v>
+        <v>0.785</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.799</v>
+        <v>0.315</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.089</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.417</v>
+        <v>0.187</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.047</v>
+        <v>0.649</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5928</v>
+        <v>0.2574</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.6237</v>
+        <v>0.2796</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.5998</v>
+        <v>0.3268</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.32505</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.53125</v>
+        <v>0.21875</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.48614</v>
+        <v>0.19169</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.4472</v>
+        <v>0.264</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.549</v>
+        <v>0.235</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8623</v>
+        <v>0.5243</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.481</v>
+        <v>0.1845</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.548</v>
+        <v>0.33</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.4225</v>
+        <v>0.145</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.2955</v>
+        <v>0.0835</v>
       </c>
       <c r="AR3" t="n">
         <v>0.05</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.948</v>
+        <v>1.42</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="AU3" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="AW3" t="n">
         <v>1.25</v>
       </c>
-      <c r="AV3" t="n">
-        <v>0.5998</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AX3" t="n">
-        <v>0.97228</v>
+        <v>0.38338</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.4851</v>
+        <v>0.2867</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.08333</v>
+        <v>0.05</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.948</v>
+        <v>1.42</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.98614</v>
+        <v>1.44169</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.031246</v>
+        <v>1.468753</v>
       </c>
       <c r="BD3" t="n">
         <v>0.05</v>
       </c>
       <c r="BE3" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>6701-04-04</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>90 deg Bent-Tube Swivel Elbow, male JIC -04 x female JIC swivel -04</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>6701</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>7/16-20 (male JIC 37 deg)</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>7/16-20 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>1.250</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>1.420</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.354</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21: M1 L1 CHEX HEXL NUTHEX NOSETIP D TUBEOD RB] Brennan CAD record 6701-04-04 decoded on BRENNAN_6701-08-08.stp (tools/_out/groupD_20261021 README s2): M1 = M, L1 = L - F - J + LN (nut face), NOSETIP = LN - F - J, RB = R; catalog TFA-p038-t02 M / L / C1 / C2 = record | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions | MODEL: bent-tube elbow = male JIC end piece (MS33656J chain per dash from the 2403 table, round body BODYR = hex corner radius, hex HEXB over HEXL behind the JIC end) + tube (circular sweep TUBEOD along line - arc RB - line) + female JIC swivel end (FLG61_MEAS by flange size: thickness, face O-ring groove; head OD = O) + one through bore TUBEID; the tube starts inside the hex body at the JIC end length and ends at the flange face; braze fillets, chamfers and the head hub NOT modelled; 6701 leg 2 = the female 37 deg JIC swivel end of the straights (gen_straight2 end_JICSW: SWIV_MEAS by size, nut and nose one solid), revolved about the leg-2 axis; L1 = crossing -&gt; nut face; the tube ends at the swivel body face (BODYS behind the nut face); nut hex cut from a plane at the nut face over the measured nut hex length; female UNF-2B nut thread = the straights' swivel thread (straight helical thread over the measured length TE from the nut face, base on the ASME B1.1 basic minor, 60 deg, height 0.54127 P; helix on the nut-face plane + swept cut, suppressed for the save); swivel neck dia 0.374 = the part's own body where the tube enters (NECKD@SWSK, not SWIV_MEAS)</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>Brennan record 6701-04-04: M 1.25 L 1.09 F 0.194 J 0.125 LN 0.649 C1 0.5 C2 0.563 THK 0.197 DIA 0.315 DIA6 0.167 R 0.354. Swivel shape = the straights' SWIV_MEAS (Q-TRANSFER-ENDLIB); NOSETIP from the record. Swivel neck 0.374 from the part's own STEP (BRENNAN_6701-04-04.stp: body cylinder 0.374 from the nut back (y 0.771) to the tube end (y 0.896 / 0.901) = record DIA4; SWIV_MEAS -04 neck 0.293 &lt; the 0.315 tube).</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>6701-04-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6701-06-06</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.753027</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.360844</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1082</v>
+      </c>
+      <c r="J4" t="n">
+        <v>60</v>
+      </c>
+      <c r="K4" t="n">
+        <v>37</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.556027</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.556027</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.25118</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.5953000000000001</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.581</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.50236</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.581</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.60118</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.631251</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1.631</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>6701-06-06</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>90 deg Bent-Tube Swivel Elbow, male JIC -06 x female JIC swivel -06</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>6701</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>9/16-18 (male JIC 37 deg)</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>9/16-18 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>1.350</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>1.581</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0.512</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>0.413</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21: M1 L1 CHEX HEXL NUTHEX NOSETIP D TUBEOD RB] Brennan CAD record 6701-06-06 decoded on BRENNAN_6701-08-08.stp (tools/_out/groupD_20261021 README s2): M1 = M, L1 = L - F - J + LN (nut face), NOSETIP = LN - F - J, RB = R; catalog TFA-p038-t02 M / L / C1 / C2 = record | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions | MODEL: bent-tube elbow = male JIC end piece (MS33656J chain per dash from the 2403 table, round body BODYR = hex corner radius, hex HEXB over HEXL behind the JIC end) + tube (circular sweep TUBEOD along line - arc RB - line) + female JIC swivel end (FLG61_MEAS by flange size: thickness, face O-ring groove; head OD = O) + one through bore TUBEID; the tube starts inside the hex body at the JIC end length and ends at the flange face; braze fillets, chamfers and the head hub NOT modelled; 6701 leg 2 = the female 37 deg JIC swivel end of the straights (gen_straight2 end_JICSW: SWIV_MEAS by size, nut and nose one solid), revolved about the leg-2 axis; L1 = crossing -&gt; nut face; the tube ends at the swivel body face (BODYS behind the nut face); nut hex cut from a plane at the nut face over the measured nut hex length; female UNF-2B nut thread = the straights' swivel thread (straight helical thread over the measured length TE from the nut face, base on the ASME B1.1 basic minor, 60 deg, height 0.54127 P; helix on the nut-face plane + swept cut, suppressed for the save); swivel neck dia 0.494 = the part's own body where the tube enters (NECKD@SWSK, not SWIV_MEAS)</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>Brennan record 6701-06-06: M 1.35 L 1.22 F 0.234 J 0.14 LN 0.735 C1 0.625 C2 0.688 THK 0.197 DIA 0.413 DIA6 0.256 R 0.512. Swivel shape = the straights' SWIV_MEAS (Q-TRANSFER-ENDLIB); NOSETIP from the record. Swivel neck 0.494 from the part's own STEP (BRENNAN_6701-06-06.stp: body cylinder 0.494 from the nut back (y 0.846) to the tube end (y 0.986 / 0.995) = record DIA4; SWIV_MEAS -06 neck 0.412 &lt; the 0.413 tube).</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>6701-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>6701-12-12</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.139997</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.649519</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="J5" t="n">
+        <v>60</v>
+      </c>
+      <c r="K5" t="n">
+        <v>37</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.7045</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.863997</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.863997</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.319</v>
       </c>
-      <c r="BF3" t="n">
+      <c r="W5" t="n">
         <v>1.181</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="X5" t="n">
         <v>2.5</v>
       </c>
-      <c r="BH3" t="n">
+      <c r="Y5" t="n">
+        <v>1.909</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.5928</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.6237</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.7216900000000001</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.4472</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.8623</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.948</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.97228</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.4851</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.948</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>2.98614</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.031246</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.181</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH5" t="n">
         <v>2.998</v>
       </c>
-      <c r="BI3" t="n">
+      <c r="BI5" t="n">
         <v>0.591</v>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>6701-12-12</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>90 deg Bent-Tube Swivel Elbow, male JIC -12 x female JIC swivel -12</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>6701</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>1 1/16-12 (male JIC 37 deg)</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>2.500</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>2.948</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>1.181</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>0.799</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>[BRENNAN-CAD 2026-10-21: M1 L1 CHEX HEXL NUTHEX NOSETIP D TUBEOD RB] Brennan CAD record 6701-12-12 decoded on BRENNAN_6701-08-08.stp (tools/_out/groupD_20261021 README s2): M1 = M, L1 = L - F - J + LN (nut face), NOSETIP = LN - F - J, RB = R; catalog TFA-p038-t02 M / L / C1 / C2 = record | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions | MODEL: bent-tube elbow = male JIC end piece (MS33656J chain per dash from the 2403 table, round body BODYR = hex corner radius, hex HEXB over HEXL behind the JIC end) + tube (circular sweep TUBEOD along line - arc RB - line) + female JIC swivel end (FLG61_MEAS by flange size: thickness, face O-ring groove; head OD = O) + one through bore TUBEID; the tube starts inside the hex body at the JIC end length and ends at the flange face; braze fillets, chamfers and the head hub NOT modelled; 6701 leg 2 = the female 37 deg JIC swivel end of the straights (gen_straight2 end_JICSW: SWIV_MEAS by size, nut and nose one solid), revolved about the leg-2 axis; L1 = crossing -&gt; nut face; the tube ends at the swivel body face (BODYS behind the nut face); nut hex cut from a plane at the nut face over the measured nut hex length; female UNF-2B nut thread = the straights' swivel thread (straight helical thread over the measured length TE from the nut face, base on the ASME B1.1 basic minor, 60 deg, height 0.54127 P; helix on the nut-face plane + swept cut, suppressed for the save)</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>Brennan record 6701-12-12: M 2.5 L 2.4 F 0.314 J 0.185 LN 1.047 C1 1.125 C2 1.25 THK 0.276 DIA 0.799 DIA6 0.591 R 1.181. Swivel shape = the straights' SWIV_MEAS (Q-TRANSFER-ENDLIB); NOSETIP from the record.</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>6701-12-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>6701-20-20</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.272952</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.977454</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="J6" t="n">
+        <v>60</v>
+      </c>
+      <c r="K6" t="n">
+        <v>37</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.7986</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.693</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.957952</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.957952</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.9889</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.1547</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.335</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.53478</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.335</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4.02739</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4.072496</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>4.385</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>6701-20-20</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>90 deg Bent-Tube Swivel Elbow, male JIC -20 x female JIC swivel -20</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>6701</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (male JIC 37 deg)</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>3.260</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>4.335</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>1.890</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>1.260</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21: M1 L1 CHEX HEXL NUTHEX NOSETIP D TUBEOD RB] Brennan CAD record 6701-20-20 decoded on BRENNAN_6701-08-08.stp (tools/_out/groupD_20261021 README s2): M1 = M, L1 = L - F - J + LN (nut face), NOSETIP = LN - F - J, RB = R; catalog TFA-p038-t02 M / L / C1 / C2 = record | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions | MODEL: bent-tube elbow = male JIC end piece (MS33656J chain per dash from the 2403 table, round body BODYR = hex corner radius, hex HEXB over HEXL behind the JIC end) + tube (circular sweep TUBEOD along line - arc RB - line) + female JIC swivel end (FLG61_MEAS by flange size: thickness, face O-ring groove; head OD = O) + one through bore TUBEID; the tube starts inside the hex body at the JIC end length and ends at the flange face; braze fillets, chamfers and the head hub NOT modelled; 6701 leg 2 = the female 37 deg JIC swivel end of the straights (gen_straight2 end_JICSW: SWIV_MEAS by size, nut and nose one solid), revolved about the leg-2 axis; L1 = crossing -&gt; nut face; the tube ends at the swivel body face (BODYS behind the nut face); nut hex cut from a plane at the nut face over the measured nut hex length; female UNF-2B nut thread = the straights' swivel thread (straight helical thread over the measured length TE from the nut face, base on the ASME B1.1 basic minor, 60 deg, height 0.54127 P; helix on the nut-face plane + swept cut, suppressed for the save)</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>Brennan record 6701-20-20: M 3.26 L 3.75 F 0.37 J 0.19 LN 1.145 C1 1.693 C2 2.0 THK 0.315 DIA 1.26 DIA6 1.024 R 1.89. Swivel shape = the straights' SWIV_MEAS (Q-TRANSFER-ENDLIB); NOSETIP from the record. BRENNAN_6701-20-20.stp: JIC tip x -3.260 = M 3.26 (CAD record); the TFA catalog p38 M 2.750 is a misprint; nut face y 4.335 = L - F - J + LN; torus R 1.890, tube 1.260 / 1.024.</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>6701-20-20</t>
         </is>
       </c>
     </row>
